--- a/exports/trend_1d/ASTRAL_full_report.xlsx
+++ b/exports/trend_1d/ASTRAL_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q69"/>
+  <dimension ref="A1:U69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,19 +557,19 @@
         <v>9.029999999999999</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>42110</v>
+        <v>42111</v>
       </c>
       <c r="H2" t="n">
-        <v>206.5</v>
+        <v>206.3</v>
       </c>
       <c r="I2" t="n">
         <v>206.4866484752348</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="K2" t="n">
-        <v>21.4</v>
+        <v>21.28</v>
       </c>
       <c r="L2" t="n">
         <v>5.09</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>60</v>
+        <v>61</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>42033</v>
+      </c>
+      <c r="S2" t="b">
+        <v>1</v>
+      </c>
+      <c r="T2" t="n">
+        <v>4</v>
+      </c>
+      <c r="U2" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="3">
@@ -591,19 +626,19 @@
         <v>19.27</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>42219</v>
+        <v>42220</v>
       </c>
       <c r="H3" t="n">
-        <v>170.15</v>
+        <v>184.35</v>
       </c>
       <c r="I3" t="n">
         <v>183.6663469906934</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="K3" t="n">
-        <v>17.52</v>
+        <v>10.64</v>
       </c>
       <c r="L3" t="n">
         <v>4.87</v>
@@ -612,7 +647,7 @@
         <v>3.63</v>
       </c>
       <c r="N3" t="n">
-        <v>5.32</v>
+        <v>8.35</v>
       </c>
       <c r="O3" t="n">
         <v>-0.1</v>
@@ -621,7 +656,19 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>76</v>
+        <v>77</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>42124</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>5</v>
+      </c>
+      <c r="U3" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="4">
@@ -648,19 +695,19 @@
         <v>12.6</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>42384</v>
+        <v>42387</v>
       </c>
       <c r="H4" t="n">
-        <v>189.45</v>
+        <v>185.2</v>
       </c>
       <c r="I4" t="n">
         <v>186.3187194070406</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="K4" t="n">
-        <v>2.77</v>
+        <v>0.46</v>
       </c>
       <c r="L4" t="n">
         <v>8.73</v>
@@ -678,7 +725,19 @@
         <v>1</v>
       </c>
       <c r="Q4" t="n">
-        <v>112</v>
+        <v>113</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>42243</v>
+      </c>
+      <c r="S4" t="b">
+        <v>1</v>
+      </c>
+      <c r="T4" t="n">
+        <v>6</v>
+      </c>
+      <c r="U4" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="5">
@@ -705,19 +764,19 @@
         <v>10.85</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>42439</v>
+        <v>42440</v>
       </c>
       <c r="H5" t="n">
-        <v>167.95</v>
+        <v>180.55</v>
       </c>
       <c r="I5" t="n">
         <v>179.672865827643</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="K5" t="n">
-        <v>9.31</v>
+        <v>2.51</v>
       </c>
       <c r="L5" t="n">
         <v>4.75</v>
@@ -726,7 +785,7 @@
         <v>3.15</v>
       </c>
       <c r="N5" t="n">
-        <v>4.49</v>
+        <v>7.5</v>
       </c>
       <c r="O5" t="n">
         <v>-2.24</v>
@@ -735,7 +794,19 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>42397</v>
+      </c>
+      <c r="S5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>3</v>
+      </c>
+      <c r="U5" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -762,19 +833,19 @@
         <v>16.36</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>42621</v>
+        <v>42622</v>
       </c>
       <c r="H6" t="n">
-        <v>214.9</v>
+        <v>211.85</v>
       </c>
       <c r="I6" t="n">
         <v>212.0059644443523</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="K6" t="n">
-        <v>19.03</v>
+        <v>17.34</v>
       </c>
       <c r="L6" t="n">
         <v>8.06</v>
@@ -792,7 +863,19 @@
         <v>1</v>
       </c>
       <c r="Q6" t="n">
-        <v>122</v>
+        <v>123</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>42460</v>
+      </c>
+      <c r="S6" t="b">
+        <v>1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>7</v>
+      </c>
+      <c r="U6" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="7">
@@ -819,19 +902,19 @@
         <v>9.619999999999999</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>42766</v>
+        <v>42767</v>
       </c>
       <c r="H7" t="n">
-        <v>174.3</v>
+        <v>187.1</v>
       </c>
       <c r="I7" t="n">
         <v>185.6996582354092</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="K7" t="n">
-        <v>17.72</v>
+        <v>11.68</v>
       </c>
       <c r="L7" t="n">
         <v>3.54</v>
@@ -840,7 +923,7 @@
         <v>2.53</v>
       </c>
       <c r="N7" t="n">
-        <v>4.14</v>
+        <v>7.34</v>
       </c>
       <c r="O7" t="n">
         <v>-1.42</v>
@@ -849,7 +932,19 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>97</v>
+        <v>98</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>42642</v>
+      </c>
+      <c r="S7" t="b">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>6</v>
+      </c>
+      <c r="U7" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="8">
@@ -876,19 +971,19 @@
         <v>12.92</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>42877</v>
+        <v>42878</v>
       </c>
       <c r="H8" t="n">
-        <v>249.9</v>
+        <v>246.3</v>
       </c>
       <c r="I8" t="n">
         <v>246.459633117759</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="K8" t="n">
-        <v>33.56</v>
+        <v>31.64</v>
       </c>
       <c r="L8" t="n">
         <v>7.27</v>
@@ -906,7 +1001,19 @@
         <v>1</v>
       </c>
       <c r="Q8" t="n">
-        <v>74</v>
+        <v>75</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>42789</v>
+      </c>
+      <c r="S8" t="b">
+        <v>1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>4</v>
+      </c>
+      <c r="U8" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="9">
@@ -933,22 +1040,22 @@
         <v>11.96</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>42886</v>
+        <v>42887</v>
       </c>
       <c r="H9" t="n">
-        <v>274.35</v>
+        <v>281.45</v>
       </c>
       <c r="I9" t="n">
         <v>275.7633702402945</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K9" t="n">
-        <v>-11.39</v>
+        <v>-14.27</v>
       </c>
       <c r="L9" t="n">
-        <v>12.91</v>
+        <v>14.76</v>
       </c>
       <c r="M9" t="n">
         <v>1.82</v>
@@ -963,7 +1070,19 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>42880</v>
+      </c>
+      <c r="S9" t="b">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -990,19 +1109,19 @@
         <v>13.95</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>42930</v>
+        <v>42933</v>
       </c>
       <c r="H10" t="n">
-        <v>301.95</v>
+        <v>290.25</v>
       </c>
       <c r="I10" t="n">
         <v>290.5602206022133</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="K10" t="n">
-        <v>7.28</v>
+        <v>3.13</v>
       </c>
       <c r="L10" t="n">
         <v>4.87</v>
@@ -1011,7 +1130,7 @@
         <v>1.78</v>
       </c>
       <c r="N10" t="n">
-        <v>3.49</v>
+        <v>3.87</v>
       </c>
       <c r="O10" t="n">
         <v>2.59</v>
@@ -1020,7 +1139,19 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>42915</v>
+      </c>
+      <c r="S10" t="b">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -1047,22 +1178,22 @@
         <v>12.41</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>42976</v>
+        <v>42977</v>
       </c>
       <c r="H11" t="n">
-        <v>303.85</v>
+        <v>307.5</v>
       </c>
       <c r="I11" t="n">
         <v>305.6989513777194</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="K11" t="n">
-        <v>-4.69</v>
+        <v>-5.94</v>
       </c>
       <c r="L11" t="n">
-        <v>5.48</v>
+        <v>6.74</v>
       </c>
       <c r="M11" t="n">
         <v>1.87</v>
@@ -1077,7 +1208,19 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>42943</v>
+      </c>
+      <c r="S11" t="b">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -1104,19 +1247,19 @@
         <v>9.710000000000001</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>43129</v>
+        <v>43130</v>
       </c>
       <c r="H12" t="n">
-        <v>362.5</v>
+        <v>350.15</v>
       </c>
       <c r="I12" t="n">
         <v>353.2621938337155</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="K12" t="n">
-        <v>17.89</v>
+        <v>13.87</v>
       </c>
       <c r="L12" t="n">
         <v>1.67</v>
@@ -1125,7 +1268,7 @@
         <v>1.18</v>
       </c>
       <c r="N12" t="n">
-        <v>2.24</v>
+        <v>3.41</v>
       </c>
       <c r="O12" t="n">
         <v>1.2</v>
@@ -1134,7 +1277,19 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>104</v>
+        <v>105</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>42978</v>
+      </c>
+      <c r="S12" t="b">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>7</v>
+      </c>
+      <c r="U12" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="13">
@@ -1161,28 +1316,28 @@
         <v>10.52</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>43157</v>
+        <v>43158</v>
       </c>
       <c r="H13" t="n">
-        <v>368.95</v>
+        <v>395</v>
       </c>
       <c r="I13" t="n">
         <v>384.8910562672689</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K13" t="n">
-        <v>-5.37</v>
+        <v>-12.81</v>
       </c>
       <c r="L13" t="n">
-        <v>10.44</v>
+        <v>14.85</v>
       </c>
       <c r="M13" t="n">
         <v>2.5</v>
       </c>
       <c r="N13" t="n">
-        <v>4.4</v>
+        <v>7.06</v>
       </c>
       <c r="O13" t="n">
         <v>-3.41</v>
@@ -1191,7 +1346,19 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>43153</v>
+      </c>
+      <c r="S13" t="b">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -1218,19 +1385,19 @@
         <v>15.39</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>43364</v>
+        <v>43367</v>
       </c>
       <c r="H14" t="n">
-        <v>485</v>
+        <v>457.75</v>
       </c>
       <c r="I14" t="n">
         <v>465.3678375318869</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="K14" t="n">
-        <v>22.78</v>
+        <v>15.89</v>
       </c>
       <c r="L14" t="n">
         <v>5.54</v>
@@ -1239,7 +1406,7 @@
         <v>1.49</v>
       </c>
       <c r="N14" t="n">
-        <v>3.27</v>
+        <v>5.62</v>
       </c>
       <c r="O14" t="n">
         <v>7.06</v>
@@ -1248,7 +1415,19 @@
         <v>1</v>
       </c>
       <c r="Q14" t="n">
-        <v>141</v>
+        <v>142</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>43187</v>
+      </c>
+      <c r="S14" t="b">
+        <v>1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>7</v>
+      </c>
+      <c r="U14" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="15">
@@ -1275,19 +1454,19 @@
         <v>14.09</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>43404</v>
+        <v>43405</v>
       </c>
       <c r="H15" t="n">
-        <v>443.85</v>
+        <v>453.95</v>
       </c>
       <c r="I15" t="n">
         <v>445.9400479147803</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="K15" t="n">
-        <v>3.04</v>
+        <v>0.83</v>
       </c>
       <c r="L15" t="n">
         <v>6.22</v>
@@ -1305,7 +1484,19 @@
         <v>1</v>
       </c>
       <c r="Q15" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>43370</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>3</v>
+      </c>
+      <c r="U15" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="16">
@@ -1332,19 +1523,19 @@
         <v>16</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>43486</v>
+        <v>43487</v>
       </c>
       <c r="H16" t="n">
-        <v>488.35</v>
+        <v>472.5</v>
       </c>
       <c r="I16" t="n">
         <v>487.8689739459437</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="K16" t="n">
-        <v>7.58</v>
+        <v>4.09</v>
       </c>
       <c r="L16" t="n">
         <v>6.23</v>
@@ -1362,7 +1553,19 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>54</v>
+        <v>55</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>43433</v>
+      </c>
+      <c r="S16" t="b">
+        <v>1</v>
+      </c>
+      <c r="T16" t="n">
+        <v>3</v>
+      </c>
+      <c r="U16" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="17">
@@ -1389,22 +1592,22 @@
         <v>11.64</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>43501</v>
+        <v>43502</v>
       </c>
       <c r="H17" t="n">
-        <v>515.9</v>
+        <v>529.8</v>
       </c>
       <c r="I17" t="n">
         <v>520.2317541133102</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K17" t="n">
-        <v>-9.19</v>
+        <v>-12.13</v>
       </c>
       <c r="L17" t="n">
-        <v>12.37</v>
+        <v>14.29</v>
       </c>
       <c r="M17" t="n">
         <v>1.44</v>
@@ -1419,7 +1622,19 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>43496</v>
+      </c>
+      <c r="S17" t="b">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -1446,19 +1661,19 @@
         <v>11.68</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>43546</v>
+        <v>43549</v>
       </c>
       <c r="H18" t="n">
-        <v>518.25</v>
+        <v>497.55</v>
       </c>
       <c r="I18" t="n">
         <v>501.6120554855115</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="K18" t="n">
-        <v>-2.18</v>
+        <v>-6.09</v>
       </c>
       <c r="L18" t="n">
         <v>9.76</v>
@@ -1476,7 +1691,19 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>43524</v>
+      </c>
+      <c r="S18" t="b">
+        <v>1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2</v>
+      </c>
+      <c r="U18" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -1503,28 +1730,28 @@
         <v>16.97</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>43602</v>
+        <v>43605</v>
       </c>
       <c r="H19" t="n">
-        <v>530</v>
+        <v>572.65</v>
       </c>
       <c r="I19" t="n">
         <v>565.053323680008</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="K19" t="n">
-        <v>-6.52</v>
+        <v>-15.09</v>
       </c>
       <c r="L19" t="n">
-        <v>14.35</v>
+        <v>15.76</v>
       </c>
       <c r="M19" t="n">
-        <v>1.99</v>
+        <v>2.4</v>
       </c>
       <c r="N19" t="n">
-        <v>3.16</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="O19" t="n">
         <v>-3.99</v>
@@ -1533,7 +1760,19 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>43552</v>
+      </c>
+      <c r="S19" t="b">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>3</v>
+      </c>
+      <c r="U19" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="20">
@@ -1560,19 +1799,19 @@
         <v>12.84</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>43669</v>
+        <v>43670</v>
       </c>
       <c r="H20" t="n">
-        <v>556.6</v>
+        <v>539.8</v>
       </c>
       <c r="I20" t="n">
         <v>551.4643638077863</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="K20" t="n">
-        <v>-2.8</v>
+        <v>-5.74</v>
       </c>
       <c r="L20" t="n">
         <v>8.619999999999999</v>
@@ -1590,7 +1829,19 @@
         <v>1</v>
       </c>
       <c r="Q20" t="n">
-        <v>46</v>
+        <v>47</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>43615</v>
+      </c>
+      <c r="S20" t="b">
+        <v>1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>3</v>
+      </c>
+      <c r="U20" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="21">
@@ -1617,22 +1868,22 @@
         <v>10.91</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>43706</v>
+        <v>43707</v>
       </c>
       <c r="H21" t="n">
-        <v>583.45</v>
+        <v>595.55</v>
       </c>
       <c r="I21" t="n">
         <v>594.0689770878215</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K21" t="n">
-        <v>-8.09</v>
+        <v>-10.33</v>
       </c>
       <c r="L21" t="n">
-        <v>10.52</v>
+        <v>10.93</v>
       </c>
       <c r="M21" t="n">
         <v>2.16</v>
@@ -1647,7 +1898,19 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>43671</v>
+      </c>
+      <c r="S21" t="b">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>3</v>
+      </c>
+      <c r="U21" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="22">
@@ -1674,19 +1937,19 @@
         <v>9.529999999999999</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>43901</v>
+        <v>43902</v>
       </c>
       <c r="H22" t="n">
-        <v>649.8</v>
+        <v>581.15</v>
       </c>
       <c r="I22" t="n">
         <v>628.0047677733448</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="K22" t="n">
-        <v>9.109999999999999</v>
+        <v>-2.42</v>
       </c>
       <c r="L22" t="n">
         <v>9.699999999999999</v>
@@ -1695,7 +1958,7 @@
         <v>5.29</v>
       </c>
       <c r="N22" t="n">
-        <v>5.81</v>
+        <v>10.56</v>
       </c>
       <c r="O22" t="n">
         <v>2.07</v>
@@ -1704,7 +1967,19 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>131</v>
+        <v>132</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>43734</v>
+      </c>
+      <c r="S22" t="b">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>7</v>
+      </c>
+      <c r="U22" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="23">
@@ -1731,19 +2006,19 @@
         <v>17.34</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>43983</v>
+        <v>43984</v>
       </c>
       <c r="H23" t="n">
-        <v>525.55</v>
+        <v>534.8</v>
       </c>
       <c r="I23" t="n">
         <v>533.5142027241893</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="K23" t="n">
-        <v>9.57</v>
+        <v>7.98</v>
       </c>
       <c r="L23" t="n">
         <v>9.83</v>
@@ -1761,7 +2036,19 @@
         <v>1</v>
       </c>
       <c r="Q23" t="n">
-        <v>52</v>
+        <v>53</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>43916</v>
+      </c>
+      <c r="S23" t="b">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>4</v>
+      </c>
+      <c r="U23" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="24">
@@ -1788,19 +2075,19 @@
         <v>16.83</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>44095</v>
+        <v>44096</v>
       </c>
       <c r="H24" t="n">
-        <v>623.1</v>
+        <v>605.8</v>
       </c>
       <c r="I24" t="n">
         <v>609.6552128846213</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="K24" t="n">
-        <v>16.51</v>
+        <v>13.28</v>
       </c>
       <c r="L24" t="n">
         <v>10.27</v>
@@ -1818,7 +2105,19 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>80</v>
+        <v>81</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>44007</v>
+      </c>
+      <c r="S24" t="b">
+        <v>1</v>
+      </c>
+      <c r="T24" t="n">
+        <v>4</v>
+      </c>
+      <c r="U24" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="25">
@@ -1845,22 +2144,22 @@
         <v>18.31</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>44144</v>
+        <v>44145</v>
       </c>
       <c r="H25" t="n">
-        <v>678.65</v>
+        <v>718.05</v>
       </c>
       <c r="I25" t="n">
         <v>692.968680335068</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="K25" t="n">
-        <v>-12.03</v>
+        <v>-18.53</v>
       </c>
       <c r="L25" t="n">
-        <v>16.64</v>
+        <v>19.26</v>
       </c>
       <c r="M25" t="n">
         <v>2.48</v>
@@ -1875,7 +2174,19 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>44098</v>
+      </c>
+      <c r="S25" t="b">
+        <v>1</v>
+      </c>
+      <c r="T25" t="n">
+        <v>3</v>
+      </c>
+      <c r="U25" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="26">
@@ -1902,19 +2213,19 @@
         <v>12.13</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>44273</v>
+        <v>44274</v>
       </c>
       <c r="H26" t="n">
-        <v>1290.4</v>
+        <v>1256.6</v>
       </c>
       <c r="I26" t="n">
         <v>1281.904068546993</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="K26" t="n">
-        <v>79.70999999999999</v>
+        <v>75</v>
       </c>
       <c r="L26" t="n">
         <v>5.37</v>
@@ -1932,7 +2243,19 @@
         <v>1</v>
       </c>
       <c r="Q26" t="n">
-        <v>89</v>
+        <v>90</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>44161</v>
+      </c>
+      <c r="S26" t="b">
+        <v>1</v>
+      </c>
+      <c r="T26" t="n">
+        <v>5</v>
+      </c>
+      <c r="U26" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="27">
@@ -1959,22 +2282,22 @@
         <v>16.46</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>44330</v>
+        <v>44333</v>
       </c>
       <c r="H27" t="n">
-        <v>1263.55</v>
+        <v>1326.75</v>
       </c>
       <c r="I27" t="n">
         <v>1296.176541607131</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="K27" t="n">
-        <v>-0.55</v>
+        <v>-5.58</v>
       </c>
       <c r="L27" t="n">
-        <v>5.42</v>
+        <v>6.39</v>
       </c>
       <c r="M27" t="n">
         <v>2.67</v>
@@ -1989,7 +2312,19 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>44280</v>
+      </c>
+      <c r="S27" t="b">
+        <v>1</v>
+      </c>
+      <c r="T27" t="n">
+        <v>3</v>
+      </c>
+      <c r="U27" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="28">
@@ -2016,19 +2351,19 @@
         <v>13.85</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>44418</v>
+        <v>44419</v>
       </c>
       <c r="H28" t="n">
-        <v>1553.1</v>
+        <v>1478.4</v>
       </c>
       <c r="I28" t="n">
         <v>1531.089945117236</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K28" t="n">
-        <v>17.06</v>
+        <v>11.43</v>
       </c>
       <c r="L28" t="n">
         <v>4.22</v>
@@ -2037,7 +2372,7 @@
         <v>1.17</v>
       </c>
       <c r="N28" t="n">
-        <v>4.23</v>
+        <v>4.81</v>
       </c>
       <c r="O28" t="n">
         <v>5</v>
@@ -2046,7 +2381,19 @@
         <v>1</v>
       </c>
       <c r="Q28" t="n">
-        <v>61</v>
+        <v>62</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>44343</v>
+      </c>
+      <c r="S28" t="b">
+        <v>1</v>
+      </c>
+      <c r="T28" t="n">
+        <v>4</v>
+      </c>
+      <c r="U28" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="29">
@@ -2073,19 +2420,19 @@
         <v>16.96</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>44469</v>
+        <v>44470</v>
       </c>
       <c r="H29" t="n">
-        <v>1624.35</v>
+        <v>1654</v>
       </c>
       <c r="I29" t="n">
         <v>1636.363316186095</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="K29" t="n">
-        <v>-9.869999999999999</v>
+        <v>-11.88</v>
       </c>
       <c r="L29" t="n">
         <v>13.31</v>
@@ -2103,7 +2450,19 @@
         <v>1</v>
       </c>
       <c r="Q29" t="n">
-        <v>35</v>
+        <v>36</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>44434</v>
+      </c>
+      <c r="S29" t="b">
+        <v>1</v>
+      </c>
+      <c r="T29" t="n">
+        <v>3</v>
+      </c>
+      <c r="U29" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="30">
@@ -2130,28 +2489,28 @@
         <v>12.65</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>44547</v>
+        <v>44550</v>
       </c>
       <c r="H30" t="n">
-        <v>1685.05</v>
+        <v>1576.7</v>
       </c>
       <c r="I30" t="n">
         <v>1589.696978452266</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="K30" t="n">
-        <v>1.88</v>
+        <v>-4.67</v>
       </c>
       <c r="L30" t="n">
-        <v>6.35</v>
+        <v>6.36</v>
       </c>
       <c r="M30" t="n">
         <v>2.38</v>
       </c>
       <c r="N30" t="n">
-        <v>5.61</v>
+        <v>6.43</v>
       </c>
       <c r="O30" t="n">
         <v>1.83</v>
@@ -2160,7 +2519,19 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>53</v>
+        <v>54</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>44497</v>
+      </c>
+      <c r="S30" t="b">
+        <v>1</v>
+      </c>
+      <c r="T30" t="n">
+        <v>3</v>
+      </c>
+      <c r="U30" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="31">
@@ -2187,22 +2558,22 @@
         <v>13.79</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>44561</v>
+        <v>44564</v>
       </c>
       <c r="H31" t="n">
-        <v>1715.65</v>
+        <v>1753.5</v>
       </c>
       <c r="I31" t="n">
         <v>1749.643439019268</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="K31" t="n">
-        <v>-8.81</v>
+        <v>-11.21</v>
       </c>
       <c r="L31" t="n">
-        <v>10.35</v>
+        <v>12.42</v>
       </c>
       <c r="M31" t="n">
         <v>2.2</v>
@@ -2217,7 +2588,19 @@
         <v>1</v>
       </c>
       <c r="Q31" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>44560</v>
+      </c>
+      <c r="S31" t="b">
+        <v>1</v>
+      </c>
+      <c r="T31" t="n">
+        <v>2</v>
+      </c>
+      <c r="U31" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="32">
@@ -2244,28 +2627,28 @@
         <v>9.869999999999999</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>44582</v>
+        <v>44585</v>
       </c>
       <c r="H32" t="n">
-        <v>1787.2</v>
+        <v>1633.3</v>
       </c>
       <c r="I32" t="n">
         <v>1715.322865655806</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="K32" t="n">
-        <v>1.92</v>
+        <v>-6.85</v>
       </c>
       <c r="L32" t="n">
-        <v>1.91</v>
+        <v>7.8</v>
       </c>
       <c r="M32" t="n">
         <v>0.22</v>
       </c>
       <c r="N32" t="n">
-        <v>2.74</v>
+        <v>8.609999999999999</v>
       </c>
       <c r="O32" t="n">
         <v>2.21</v>
@@ -2274,7 +2657,19 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S32" t="b">
+        <v>0</v>
+      </c>
+      <c r="T32" t="n">
+        <v>1</v>
+      </c>
+      <c r="U32" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="33">
@@ -2301,19 +2696,19 @@
         <v>16.2</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>44635</v>
+        <v>44636</v>
       </c>
       <c r="H33" t="n">
-        <v>1481.05</v>
+        <v>1533.25</v>
       </c>
       <c r="I33" t="n">
         <v>1532.135597482853</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="K33" t="n">
-        <v>9.32</v>
+        <v>6.13</v>
       </c>
       <c r="L33" t="n">
         <v>9.470000000000001</v>
@@ -2331,7 +2726,19 @@
         <v>1</v>
       </c>
       <c r="Q33" t="n">
-        <v>35</v>
+        <v>36</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S33" t="b">
+        <v>1</v>
+      </c>
+      <c r="T33" t="n">
+        <v>3</v>
+      </c>
+      <c r="U33" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="34">
@@ -2358,28 +2765,28 @@
         <v>12.52</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>44686</v>
+        <v>44687</v>
       </c>
       <c r="H34" t="n">
-        <v>1523.65</v>
+        <v>1447.9</v>
       </c>
       <c r="I34" t="n">
         <v>1473.490327326191</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="K34" t="n">
-        <v>-0.63</v>
+        <v>-5.57</v>
       </c>
       <c r="L34" t="n">
-        <v>5.84</v>
+        <v>8.789999999999999</v>
       </c>
       <c r="M34" t="n">
-        <v>0.72</v>
+        <v>2.03</v>
       </c>
       <c r="N34" t="n">
-        <v>4.06</v>
+        <v>4.97</v>
       </c>
       <c r="O34" t="n">
         <v>3.52</v>
@@ -2388,7 +2795,19 @@
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S34" t="b">
+        <v>1</v>
+      </c>
+      <c r="T34" t="n">
+        <v>3</v>
+      </c>
+      <c r="U34" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="35">
@@ -2415,19 +2834,19 @@
         <v>12.79</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>44768</v>
+        <v>44769</v>
       </c>
       <c r="H35" t="n">
-        <v>1315.8</v>
+        <v>1348.7</v>
       </c>
       <c r="I35" t="n">
         <v>1347.919453231731</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="K35" t="n">
-        <v>9.119999999999999</v>
+        <v>6.85</v>
       </c>
       <c r="L35" t="n">
         <v>3.39</v>
@@ -2445,7 +2864,19 @@
         <v>1</v>
       </c>
       <c r="Q35" t="n">
-        <v>58</v>
+        <v>59</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>44707</v>
+      </c>
+      <c r="S35" t="b">
+        <v>1</v>
+      </c>
+      <c r="T35" t="n">
+        <v>3</v>
+      </c>
+      <c r="U35" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="36">
@@ -2472,19 +2903,19 @@
         <v>9.57</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>44827</v>
+        <v>44830</v>
       </c>
       <c r="H36" t="n">
-        <v>1741.3</v>
+        <v>1660.65</v>
       </c>
       <c r="I36" t="n">
         <v>1720.584003524437</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="K36" t="n">
-        <v>29.11</v>
+        <v>23.13</v>
       </c>
       <c r="L36" t="n">
         <v>3.67</v>
@@ -2502,7 +2933,19 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>44770</v>
+      </c>
+      <c r="S36" t="b">
+        <v>1</v>
+      </c>
+      <c r="T36" t="n">
+        <v>3</v>
+      </c>
+      <c r="U36" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="37">
@@ -2529,19 +2972,19 @@
         <v>16.07</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>44896</v>
+        <v>44897</v>
       </c>
       <c r="H37" t="n">
-        <v>1446.75</v>
+        <v>1517.55</v>
       </c>
       <c r="I37" t="n">
         <v>1516.282050118378</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="K37" t="n">
-        <v>12.88</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="L37" t="n">
         <v>4.36</v>
@@ -2550,7 +2993,7 @@
         <v>2.05</v>
       </c>
       <c r="N37" t="n">
-        <v>4.08</v>
+        <v>4.89</v>
       </c>
       <c r="O37" t="n">
         <v>-4.63</v>
@@ -2559,7 +3002,19 @@
         <v>1</v>
       </c>
       <c r="Q37" t="n">
-        <v>46</v>
+        <v>47</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S37" t="b">
+        <v>1</v>
+      </c>
+      <c r="T37" t="n">
+        <v>4</v>
+      </c>
+      <c r="U37" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="38">
@@ -2586,28 +3041,28 @@
         <v>9.52</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>44917</v>
+        <v>44918</v>
       </c>
       <c r="H38" t="n">
-        <v>1478.3</v>
+        <v>1424.3</v>
       </c>
       <c r="I38" t="n">
         <v>1474.050161708244</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K38" t="n">
-        <v>-2.59</v>
+        <v>-6.14</v>
       </c>
       <c r="L38" t="n">
-        <v>4.96</v>
+        <v>6.78</v>
       </c>
       <c r="M38" t="n">
         <v>0.85</v>
       </c>
       <c r="N38" t="n">
-        <v>2.25</v>
+        <v>3.65</v>
       </c>
       <c r="O38" t="n">
         <v>4.89</v>
@@ -2616,7 +3071,19 @@
         <v>1</v>
       </c>
       <c r="Q38" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S38" t="b">
+        <v>0</v>
+      </c>
+      <c r="T38" t="n">
+        <v>1</v>
+      </c>
+      <c r="U38" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="39">
@@ -2643,19 +3110,19 @@
         <v>10.73</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>45026</v>
+        <v>45027</v>
       </c>
       <c r="H39" t="n">
-        <v>1404.2</v>
+        <v>1438.4</v>
       </c>
       <c r="I39" t="n">
         <v>1420.800438275784</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="K39" t="n">
-        <v>1.41</v>
+        <v>-0.99</v>
       </c>
       <c r="L39" t="n">
         <v>12.44</v>
@@ -2673,7 +3140,19 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>72</v>
+        <v>73</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S39" t="b">
+        <v>1</v>
+      </c>
+      <c r="T39" t="n">
+        <v>5</v>
+      </c>
+      <c r="U39" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="40">
@@ -2700,19 +3179,19 @@
         <v>8.81</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>45112</v>
+        <v>45113</v>
       </c>
       <c r="H40" t="n">
-        <v>1869.15</v>
+        <v>1842.05</v>
       </c>
       <c r="I40" t="n">
         <v>1862.517495508088</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K40" t="n">
-        <v>29.95</v>
+        <v>28.06</v>
       </c>
       <c r="L40" t="n">
         <v>3.81</v>
@@ -2730,7 +3209,19 @@
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>59</v>
+        <v>60</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>45043</v>
+      </c>
+      <c r="S40" t="b">
+        <v>1</v>
+      </c>
+      <c r="T40" t="n">
+        <v>4</v>
+      </c>
+      <c r="U40" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="41">
@@ -2757,22 +3248,22 @@
         <v>8.27</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>45135</v>
+        <v>45138</v>
       </c>
       <c r="H41" t="n">
-        <v>1909.25</v>
+        <v>1969.35</v>
       </c>
       <c r="I41" t="n">
         <v>1928.467304773728</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="K41" t="n">
-        <v>-3.65</v>
+        <v>-6.91</v>
       </c>
       <c r="L41" t="n">
-        <v>5.78</v>
+        <v>8.029999999999999</v>
       </c>
       <c r="M41" t="n">
         <v>1.49</v>
@@ -2787,7 +3278,19 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>45134</v>
+      </c>
+      <c r="S41" t="b">
+        <v>1</v>
+      </c>
+      <c r="T41" t="n">
+        <v>2</v>
+      </c>
+      <c r="U41" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="42">
@@ -2814,28 +3317,28 @@
         <v>10.3</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>45190</v>
+        <v>45191</v>
       </c>
       <c r="H42" t="n">
-        <v>1893.15</v>
+        <v>1841.05</v>
       </c>
       <c r="I42" t="n">
         <v>1864.580276224544</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="K42" t="n">
-        <v>-3.87</v>
+        <v>-6.51</v>
       </c>
       <c r="L42" t="n">
-        <v>5.18</v>
+        <v>6.89</v>
       </c>
       <c r="M42" t="n">
         <v>2.19</v>
       </c>
       <c r="N42" t="n">
-        <v>2.59</v>
+        <v>2.75</v>
       </c>
       <c r="O42" t="n">
         <v>3.15</v>
@@ -2844,7 +3347,19 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>45169</v>
+      </c>
+      <c r="S42" t="b">
+        <v>1</v>
+      </c>
+      <c r="T42" t="n">
+        <v>2</v>
+      </c>
+      <c r="U42" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="43">
@@ -2871,19 +3386,19 @@
         <v>8.300000000000001</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>45250</v>
+        <v>45251</v>
       </c>
       <c r="H43" t="n">
-        <v>1892.15</v>
+        <v>1941.4</v>
       </c>
       <c r="I43" t="n">
         <v>1940.907924636405</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="K43" t="n">
-        <v>-2.78</v>
+        <v>-5.45</v>
       </c>
       <c r="L43" t="n">
         <v>7.53</v>
@@ -2901,7 +3416,19 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>45197</v>
+      </c>
+      <c r="S43" t="b">
+        <v>1</v>
+      </c>
+      <c r="T43" t="n">
+        <v>3</v>
+      </c>
+      <c r="U43" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="44">
@@ -2928,28 +3455,28 @@
         <v>6.78</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>45279</v>
+        <v>45280</v>
       </c>
       <c r="H44" t="n">
-        <v>1908.85</v>
+        <v>1865</v>
       </c>
       <c r="I44" t="n">
         <v>1875.879559278622</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K44" t="n">
-        <v>-1.68</v>
+        <v>-3.94</v>
       </c>
       <c r="L44" t="n">
-        <v>2.85</v>
+        <v>4.57</v>
       </c>
       <c r="M44" t="n">
         <v>0.32</v>
       </c>
       <c r="N44" t="n">
-        <v>2.07</v>
+        <v>2.3</v>
       </c>
       <c r="O44" t="n">
         <v>2.6</v>
@@ -2958,7 +3485,19 @@
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S44" t="b">
+        <v>1</v>
+      </c>
+      <c r="T44" t="n">
+        <v>2</v>
+      </c>
+      <c r="U44" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="45">
@@ -2985,19 +3524,19 @@
         <v>9.91</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>45322</v>
+        <v>45323</v>
       </c>
       <c r="H45" t="n">
-        <v>1830.4</v>
+        <v>1889.2</v>
       </c>
       <c r="I45" t="n">
         <v>1881.213934034872</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K45" t="n">
-        <v>1.86</v>
+        <v>-1.3</v>
       </c>
       <c r="L45" t="n">
         <v>4.98</v>
@@ -3015,7 +3554,19 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>45288</v>
+      </c>
+      <c r="S45" t="b">
+        <v>1</v>
+      </c>
+      <c r="T45" t="n">
+        <v>3</v>
+      </c>
+      <c r="U45" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="46">
@@ -3042,19 +3593,19 @@
         <v>9.91</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>45370</v>
+        <v>45371</v>
       </c>
       <c r="H46" t="n">
-        <v>1951.75</v>
+        <v>1904.85</v>
       </c>
       <c r="I46" t="n">
         <v>1944.419446016243</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K46" t="n">
-        <v>3.31</v>
+        <v>0.83</v>
       </c>
       <c r="L46" t="n">
         <v>3.66</v>
@@ -3072,7 +3623,19 @@
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>45351</v>
+      </c>
+      <c r="S46" t="b">
+        <v>1</v>
+      </c>
+      <c r="T46" t="n">
+        <v>2</v>
+      </c>
+      <c r="U46" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="47">
@@ -3099,28 +3662,28 @@
         <v>13.56</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>45411</v>
+        <v>45412</v>
       </c>
       <c r="H47" t="n">
-        <v>2055.5</v>
+        <v>2118.1</v>
       </c>
       <c r="I47" t="n">
         <v>2104.689458455702</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="K47" t="n">
-        <v>-7.91</v>
+        <v>-11.2</v>
       </c>
       <c r="L47" t="n">
-        <v>10.24</v>
+        <v>12.84</v>
       </c>
       <c r="M47" t="n">
         <v>1.76</v>
       </c>
       <c r="N47" t="n">
-        <v>2.79</v>
+        <v>3.05</v>
       </c>
       <c r="O47" t="n">
         <v>-2.4</v>
@@ -3129,7 +3692,19 @@
         <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>45379</v>
+      </c>
+      <c r="S47" t="b">
+        <v>1</v>
+      </c>
+      <c r="T47" t="n">
+        <v>3</v>
+      </c>
+      <c r="U47" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="48">
@@ -3156,19 +3731,19 @@
         <v>9.279999999999999</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>45430</v>
+        <v>45433</v>
       </c>
       <c r="H48" t="n">
-        <v>2193.75</v>
+        <v>2078.2</v>
       </c>
       <c r="I48" t="n">
         <v>2104.890163872707</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="K48" t="n">
-        <v>3.57</v>
+        <v>-1.88</v>
       </c>
       <c r="L48" t="n">
         <v>4.49</v>
@@ -3177,7 +3752,7 @@
         <v>1.58</v>
       </c>
       <c r="N48" t="n">
-        <v>4.74</v>
+        <v>5.27</v>
       </c>
       <c r="O48" t="n">
         <v>3.05</v>
@@ -3186,7 +3761,19 @@
         <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S48" t="b">
+        <v>0</v>
+      </c>
+      <c r="T48" t="n">
+        <v>1</v>
+      </c>
+      <c r="U48" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -3213,22 +3800,22 @@
         <v>14.17</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>45464</v>
+        <v>45467</v>
       </c>
       <c r="H49" t="n">
-        <v>2273.65</v>
+        <v>2384.4</v>
       </c>
       <c r="I49" t="n">
         <v>2277.911986995795</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="K49" t="n">
-        <v>-9.4</v>
+        <v>-14.73</v>
       </c>
       <c r="L49" t="n">
-        <v>10.72</v>
+        <v>15.17</v>
       </c>
       <c r="M49" t="n">
         <v>2.44</v>
@@ -3243,7 +3830,19 @@
         <v>1</v>
       </c>
       <c r="Q49" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S49" t="b">
+        <v>1</v>
+      </c>
+      <c r="T49" t="n">
+        <v>2</v>
+      </c>
+      <c r="U49" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="50">
@@ -3270,19 +3869,19 @@
         <v>12.27</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>45496</v>
+        <v>45497</v>
       </c>
       <c r="H50" t="n">
-        <v>2236.55</v>
+        <v>2199.55</v>
       </c>
       <c r="I50" t="n">
         <v>2211.287168864259</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K50" t="n">
-        <v>-6.2</v>
+        <v>-7.75</v>
       </c>
       <c r="L50" t="n">
         <v>8.65</v>
@@ -3300,7 +3899,19 @@
         <v>1</v>
       </c>
       <c r="Q50" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S50" t="b">
+        <v>1</v>
+      </c>
+      <c r="T50" t="n">
+        <v>2</v>
+      </c>
+      <c r="U50" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="51">
@@ -3327,25 +3938,25 @@
         <v>9.699999999999999</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>45559</v>
+        <v>45560</v>
       </c>
       <c r="H51" t="n">
-        <v>2008.95</v>
+        <v>2024.95</v>
       </c>
       <c r="I51" t="n">
         <v>2011.242647628799</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="K51" t="n">
-        <v>8.67</v>
+        <v>7.94</v>
       </c>
       <c r="L51" t="n">
         <v>1.84</v>
       </c>
       <c r="M51" t="n">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="N51" t="n">
         <v>3.48</v>
@@ -3357,7 +3968,19 @@
         <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>45498</v>
+      </c>
+      <c r="S51" t="b">
+        <v>1</v>
+      </c>
+      <c r="T51" t="n">
+        <v>3</v>
+      </c>
+      <c r="U51" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="52">
@@ -3384,22 +4007,22 @@
         <v>6.21</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>45568</v>
+        <v>45569</v>
       </c>
       <c r="H52" t="n">
-        <v>1918.95</v>
+        <v>1893.15</v>
       </c>
       <c r="I52" t="n">
         <v>1899.214633251671</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K52" t="n">
-        <v>-5.23</v>
+        <v>-6.51</v>
       </c>
       <c r="L52" t="n">
-        <v>5.8</v>
+        <v>7.25</v>
       </c>
       <c r="M52" t="n">
         <v>1.49</v>
@@ -3414,7 +4037,19 @@
         <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>45561</v>
+      </c>
+      <c r="S52" t="b">
+        <v>1</v>
+      </c>
+      <c r="T52" t="n">
+        <v>2</v>
+      </c>
+      <c r="U52" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="53">
@@ -3441,19 +4076,19 @@
         <v>7.23</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>45628</v>
+        <v>45629</v>
       </c>
       <c r="H53" t="n">
-        <v>1816.3</v>
+        <v>1845.7</v>
       </c>
       <c r="I53" t="n">
         <v>1842.240973149318</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="K53" t="n">
-        <v>4.06</v>
+        <v>2.51</v>
       </c>
       <c r="L53" t="n">
         <v>1.68</v>
@@ -3471,7 +4106,19 @@
         <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S53" t="b">
+        <v>1</v>
+      </c>
+      <c r="T53" t="n">
+        <v>3</v>
+      </c>
+      <c r="U53" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="54">
@@ -3498,28 +4145,28 @@
         <v>7.23</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>45645</v>
+        <v>45646</v>
       </c>
       <c r="H54" t="n">
-        <v>1782.3</v>
+        <v>1734.6</v>
       </c>
       <c r="I54" t="n">
         <v>1748.740232380448</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K54" t="n">
-        <v>-3.44</v>
+        <v>-6.02</v>
       </c>
       <c r="L54" t="n">
-        <v>4.43</v>
+        <v>6.39</v>
       </c>
       <c r="M54" t="n">
         <v>0.57</v>
       </c>
       <c r="N54" t="n">
-        <v>1.45</v>
+        <v>2.68</v>
       </c>
       <c r="O54" t="n">
         <v>1.62</v>
@@ -3528,7 +4175,19 @@
         <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>45652</v>
+      </c>
+      <c r="S54" t="b">
+        <v>0</v>
+      </c>
+      <c r="T54" t="n">
+        <v>1</v>
+      </c>
+      <c r="U54" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="55">
@@ -3555,19 +4214,19 @@
         <v>8.6</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>45768</v>
+        <v>45769</v>
       </c>
       <c r="H55" t="n">
-        <v>1336.7</v>
+        <v>1368.6</v>
       </c>
       <c r="I55" t="n">
         <v>1364.219432893376</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="K55" t="n">
-        <v>22.94</v>
+        <v>21.1</v>
       </c>
       <c r="L55" t="n">
         <v>3.52</v>
@@ -3585,7 +4244,19 @@
         <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>81</v>
+        <v>82</v>
+      </c>
+      <c r="R55" s="3" t="n">
+        <v>45652</v>
+      </c>
+      <c r="S55" t="b">
+        <v>1</v>
+      </c>
+      <c r="T55" t="n">
+        <v>5</v>
+      </c>
+      <c r="U55" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="56">
@@ -3612,19 +4283,19 @@
         <v>9.99</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>45862</v>
+        <v>45863</v>
       </c>
       <c r="H56" t="n">
-        <v>1472.6</v>
+        <v>1440.2</v>
       </c>
       <c r="I56" t="n">
         <v>1453.093292409823</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K56" t="n">
-        <v>7.6</v>
+        <v>5.23</v>
       </c>
       <c r="L56" t="n">
         <v>8.67</v>
@@ -3642,7 +4313,19 @@
         <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>67</v>
+        <v>68</v>
+      </c>
+      <c r="R56" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S56" t="b">
+        <v>1</v>
+      </c>
+      <c r="T56" t="n">
+        <v>4</v>
+      </c>
+      <c r="U56" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="57">
@@ -3669,25 +4352,25 @@
         <v>7.6</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>45889</v>
+        <v>45890</v>
       </c>
       <c r="H57" t="n">
-        <v>1393.8</v>
+        <v>1421.4</v>
       </c>
       <c r="I57" t="n">
         <v>1398.786003891049</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K57" t="n">
-        <v>3.22</v>
+        <v>1.31</v>
       </c>
       <c r="L57" t="n">
         <v>2.4</v>
       </c>
       <c r="M57" t="n">
-        <v>0.8</v>
+        <v>1.81</v>
       </c>
       <c r="N57" t="n">
         <v>3.99</v>
@@ -3699,7 +4382,19 @@
         <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R57" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S57" t="b">
+        <v>1</v>
+      </c>
+      <c r="T57" t="n">
+        <v>2</v>
+      </c>
+      <c r="U57" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="58">
@@ -3726,19 +4421,19 @@
         <v>9.56</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>45926</v>
+        <v>45929</v>
       </c>
       <c r="H58" t="n">
-        <v>1373.8</v>
+        <v>1366.7</v>
       </c>
       <c r="I58" t="n">
         <v>1369.780483879662</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="K58" t="n">
-        <v>-3.35</v>
+        <v>-3.85</v>
       </c>
       <c r="L58" t="n">
         <v>5.1</v>
@@ -3756,7 +4451,19 @@
         <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R58" s="3" t="n">
+        <v>45897</v>
+      </c>
+      <c r="S58" t="b">
+        <v>1</v>
+      </c>
+      <c r="T58" t="n">
+        <v>2</v>
+      </c>
+      <c r="U58" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="59">
@@ -3783,22 +4490,22 @@
         <v>7.59</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>45958</v>
+        <v>45959</v>
       </c>
       <c r="H59" t="n">
-        <v>1450.2</v>
+        <v>1464.8</v>
       </c>
       <c r="I59" t="n">
         <v>1460.012758245335</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K59" t="n">
-        <v>-6.11</v>
+        <v>-7.18</v>
       </c>
       <c r="L59" t="n">
-        <v>6.97</v>
+        <v>7.4</v>
       </c>
       <c r="M59" t="n">
         <v>0.91</v>
@@ -3813,7 +4520,19 @@
         <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R59" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S59" t="b">
+        <v>1</v>
+      </c>
+      <c r="T59" t="n">
+        <v>3</v>
+      </c>
+      <c r="U59" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="60">
@@ -3840,28 +4559,28 @@
         <v>5.87</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>45975</v>
+        <v>45978</v>
       </c>
       <c r="H60" t="n">
-        <v>1514</v>
+        <v>1465.7</v>
       </c>
       <c r="I60" t="n">
         <v>1474.027431361504</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="K60" t="n">
-        <v>3.36</v>
+        <v>0.06</v>
       </c>
       <c r="L60" t="n">
         <v>1.69</v>
       </c>
       <c r="M60" t="n">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="N60" t="n">
-        <v>2.36</v>
+        <v>3.19</v>
       </c>
       <c r="O60" t="n">
         <v>1.01</v>
@@ -3870,7 +4589,19 @@
         <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R60" s="3" t="n">
+        <v>45986</v>
+      </c>
+      <c r="S60" t="b">
+        <v>0</v>
+      </c>
+      <c r="T60" t="n">
+        <v>1</v>
+      </c>
+      <c r="U60" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="61">
@@ -3897,19 +4628,19 @@
         <v>8.9</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>46023</v>
+        <v>46024</v>
       </c>
       <c r="H61" t="n">
-        <v>1434.9</v>
+        <v>1453.4</v>
       </c>
       <c r="I61" t="n">
         <v>1449.560011010379</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="K61" t="n">
-        <v>2.1</v>
+        <v>0.84</v>
       </c>
       <c r="L61" t="n">
         <v>3.36</v>
@@ -3927,7 +4658,19 @@
         <v>0</v>
       </c>
       <c r="Q61" t="n">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="R61" s="3" t="n">
+        <v>45986</v>
+      </c>
+      <c r="S61" t="b">
+        <v>1</v>
+      </c>
+      <c r="T61" t="n">
+        <v>3</v>
+      </c>
+      <c r="U61" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="62">
@@ -3954,28 +4697,28 @@
         <v>6.77</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>46041</v>
+        <v>46042</v>
       </c>
       <c r="H62" t="n">
-        <v>1439</v>
+        <v>1392.1</v>
       </c>
       <c r="I62" t="n">
         <v>1397.534456888633</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K62" t="n">
-        <v>-0.99</v>
+        <v>-4.22</v>
       </c>
       <c r="L62" t="n">
-        <v>2.5</v>
+        <v>4.57</v>
       </c>
       <c r="M62" t="n">
         <v>0.83</v>
       </c>
       <c r="N62" t="n">
-        <v>1.85</v>
+        <v>3.26</v>
       </c>
       <c r="O62" t="n">
         <v>1.29</v>
@@ -3984,7 +4727,19 @@
         <v>0</v>
       </c>
       <c r="Q62" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R62" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S62" t="b">
+        <v>0</v>
+      </c>
+      <c r="T62" t="n">
+        <v>1</v>
+      </c>
+      <c r="U62" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="63">
@@ -4011,25 +4766,25 @@
         <v>9.91</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>46055</v>
+        <v>46056</v>
       </c>
       <c r="H63" t="n">
-        <v>1467.6</v>
+        <v>1503.5</v>
       </c>
       <c r="I63" t="n">
         <v>1487.758340330407</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K63" t="n">
-        <v>-5.42</v>
+        <v>-8</v>
       </c>
       <c r="L63" t="n">
-        <v>7.44</v>
+        <v>8.470000000000001</v>
       </c>
       <c r="M63" t="n">
-        <v>0.77</v>
+        <v>1.66</v>
       </c>
       <c r="N63" t="n">
         <v>4.85</v>
@@ -4041,7 +4796,19 @@
         <v>0</v>
       </c>
       <c r="Q63" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R63" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S63" t="b">
+        <v>1</v>
+      </c>
+      <c r="T63" t="n">
+        <v>2</v>
+      </c>
+      <c r="U63" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="64">
@@ -4068,19 +4835,19 @@
         <v>9.390000000000001</v>
       </c>
       <c r="G64" s="1" t="n">
-        <v>46101</v>
+        <v>46104</v>
       </c>
       <c r="H64" t="n">
-        <v>1631.8</v>
+        <v>1556.3</v>
       </c>
       <c r="I64" t="n">
         <v>1567.404256213266</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="K64" t="n">
-        <v>8.529999999999999</v>
+        <v>3.51</v>
       </c>
       <c r="L64" t="n">
         <v>2.89</v>
@@ -4098,7 +4865,19 @@
         <v>0</v>
       </c>
       <c r="Q64" t="n">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="R64" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S64" t="b">
+        <v>1</v>
+      </c>
+      <c r="T64" t="n">
+        <v>2</v>
+      </c>
+      <c r="U64" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="65">
@@ -4125,19 +4904,19 @@
         <v>12.5</v>
       </c>
       <c r="G65" s="1" t="n">
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="H65" t="n">
-        <v>1413.4</v>
+        <v>1468.1</v>
       </c>
       <c r="I65" t="n">
         <v>1440.618235107956</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="K65" t="n">
-        <v>9.18</v>
+        <v>5.67</v>
       </c>
       <c r="L65" t="n">
         <v>7.82</v>
@@ -4155,7 +4934,19 @@
         <v>1</v>
       </c>
       <c r="Q65" t="n">
-        <v>82</v>
+        <v>83</v>
+      </c>
+      <c r="R65" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S65" t="b">
+        <v>1</v>
+      </c>
+      <c r="T65" t="n">
+        <v>5</v>
+      </c>
+      <c r="U65" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="66">
@@ -4182,19 +4973,19 @@
         <v>9.949999999999999</v>
       </c>
       <c r="G66" s="1" t="n">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="H66" t="n">
-        <v>1459</v>
+        <v>1411.4</v>
       </c>
       <c r="I66" t="n">
         <v>1448.705061168272</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="K66" t="n">
-        <v>-0.62</v>
+        <v>-3.86</v>
       </c>
       <c r="L66" t="n">
         <v>4.48</v>
@@ -4203,7 +4994,7 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="N66" t="n">
-        <v>2.24</v>
+        <v>3.26</v>
       </c>
       <c r="O66" t="n">
         <v>3.87</v>
@@ -4212,7 +5003,19 @@
         <v>0</v>
       </c>
       <c r="Q66" t="n">
-        <v>35</v>
+        <v>36</v>
+      </c>
+      <c r="R66" s="3" t="n">
+        <v>46231</v>
+      </c>
+      <c r="S66" t="b">
+        <v>1</v>
+      </c>
+      <c r="T66" t="n">
+        <v>3</v>
+      </c>
+      <c r="U66" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="67">
@@ -4239,19 +5042,19 @@
         <v>8.550000000000001</v>
       </c>
       <c r="G67" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="H67" t="n">
-        <v>1430.4</v>
+        <v>1442</v>
       </c>
       <c r="I67" t="n">
         <v>1438.036468198595</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="K67" t="n">
-        <v>-1.35</v>
+        <v>-2.17</v>
       </c>
       <c r="L67" t="n">
         <v>3.16</v>
@@ -4269,7 +5072,19 @@
         <v>0</v>
       </c>
       <c r="Q67" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R67" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S67" t="b">
+        <v>1</v>
+      </c>
+      <c r="T67" t="n">
+        <v>2</v>
+      </c>
+      <c r="U67" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="68">
@@ -4296,22 +5111,22 @@
         <v>8.029999999999999</v>
       </c>
       <c r="G68" s="1" t="n">
-        <v>46318</v>
+        <v>46321</v>
       </c>
       <c r="H68" t="n">
-        <v>1357</v>
+        <v>1349</v>
       </c>
       <c r="I68" t="n">
         <v>1352.242272155968</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="K68" t="n">
-        <v>-5.89</v>
+        <v>-6.45</v>
       </c>
       <c r="L68" t="n">
-        <v>6.57</v>
+        <v>7.55</v>
       </c>
       <c r="M68" t="n">
         <v>1.06</v>
@@ -4326,7 +5141,19 @@
         <v>0</v>
       </c>
       <c r="Q68" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R68" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="S68" t="b">
+        <v>0</v>
+      </c>
+      <c r="T68" t="n">
+        <v>1</v>
+      </c>
+      <c r="U68" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="69">
@@ -4377,6 +5204,14 @@
       <c r="Q69" t="n">
         <v>3</v>
       </c>
+      <c r="R69" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="S69" t="b">
+        <v>1</v>
+      </c>
+      <c r="T69" t="inlineStr"/>
+      <c r="U69" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -9335,7 +10170,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>62.7</v>
+        <v>64.2</v>
       </c>
     </row>
     <row r="6">
@@ -9345,7 +10180,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="7">
@@ -9355,7 +10190,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>206</v>
+        <v>209</v>
       </c>
     </row>
     <row r="8">
@@ -9365,7 +10200,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="9">
@@ -9375,7 +10210,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="10">
@@ -9385,7 +10220,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>124.4</v>
+        <v>125.4</v>
       </c>
     </row>
     <row r="11">
@@ -9425,7 +10260,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>4.97</v>
+        <v>1.47</v>
       </c>
     </row>
     <row r="15">
@@ -9435,7 +10270,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>8.949999999999999</v>
+        <v>5.29</v>
       </c>
     </row>
     <row r="16">
@@ -9445,7 +10280,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.87</v>
+        <v>-2.46</v>
       </c>
     </row>
     <row r="17">
@@ -9455,7 +10290,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>79.70999999999999</v>
+        <v>75</v>
       </c>
     </row>
     <row r="18">
@@ -9465,7 +10300,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>55.2</v>
+        <v>46.3</v>
       </c>
     </row>
     <row r="19">
@@ -9475,7 +10310,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>6.52</v>
+        <v>7.24</v>
       </c>
     </row>
     <row r="20">
@@ -9485,7 +10320,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>5.54</v>
+        <v>6.74</v>
       </c>
     </row>
     <row r="21">
@@ -9495,7 +10330,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>16.64</v>
+        <v>19.26</v>
       </c>
     </row>
     <row r="22">
@@ -9505,7 +10340,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
     </row>
     <row r="23">
@@ -9525,7 +10360,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.99</v>
+        <v>2.04</v>
       </c>
     </row>
     <row r="25">
@@ -9545,7 +10380,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>4.33</v>
+        <v>4.95</v>
       </c>
     </row>
     <row r="27">
@@ -9565,7 +10400,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
     </row>
     <row r="29">
